--- a/LexIA_Diario/config/metricas_julio_2026.xlsx
+++ b/LexIA_Diario/config/metricas_julio_2026.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/Interbank/LexIA_Diario/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_1C814E6DB7975EF061BA440EDA1E6772385F6ABF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C7E1D29-FE23-4EB7-B8AD-E0ECE1CCAEC1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="resumen" sheetId="1" r:id="rId1"/>
     <sheet name="metricas_diarias" sheetId="2" r:id="rId2"/>
     <sheet name="norma_por_norma" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">norma_por_norma!$A$1:$J$94</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1350,12 +1354,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1363,7 +1367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1371,7 +1375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1379,7 +1383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -1387,7 +1391,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1395,7 +1399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1403,7 +1407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1411,7 +1415,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1419,7 +1423,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -1427,7 +1431,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1435,7 +1439,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1443,7 +1447,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1451,7 +1455,7 @@
         <v>0.32098765432098758</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -1459,7 +1463,7 @@
         <v>0.68421052631578949</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1467,7 +1471,7 @@
         <v>0.43697478991596639</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -1475,7 +1479,7 @@
         <v>0.3708898944193062</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1483,7 +1487,7 @@
         <v>0.60277777777777775</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1499,12 +1503,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -1542,7 +1546,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1580,7 +1584,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -1618,7 +1622,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -1656,7 +1660,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>35</v>
       </c>
@@ -1694,7 +1698,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -1732,7 +1736,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1767,7 +1771,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>38</v>
       </c>
@@ -1796,7 +1800,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -1834,7 +1838,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -1872,7 +1876,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1901,7 +1905,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -1930,7 +1934,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -1959,7 +1963,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -1988,7 +1992,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>46</v>
       </c>
@@ -2026,7 +2030,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>47</v>
       </c>
@@ -2064,7 +2068,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -2099,7 +2103,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -2134,7 +2138,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -2163,7 +2167,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>51</v>
       </c>
@@ -2192,7 +2196,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>52</v>
       </c>
@@ -2230,7 +2234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -2259,7 +2263,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -2294,7 +2298,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2332,7 +2336,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>56</v>
       </c>
@@ -2367,7 +2371,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>57</v>
       </c>
@@ -2405,7 +2409,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>58</v>
       </c>
@@ -2434,7 +2438,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -2463,7 +2467,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>60</v>
       </c>
@@ -2492,7 +2496,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -2524,7 +2528,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -2560,10 +2564,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="8" max="8" width="34" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -2595,7 +2603,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2615,7 +2623,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2638,7 +2646,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2670,7 +2678,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2702,7 +2710,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2734,7 +2742,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2766,7 +2774,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -2786,7 +2794,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -2809,7 +2817,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -2832,7 +2840,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -2864,7 +2872,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -2896,7 +2904,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -2928,7 +2936,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -2960,7 +2968,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -2983,7 +2991,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -3006,7 +3014,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>34</v>
       </c>
@@ -3038,7 +3046,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -3070,7 +3078,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -3102,7 +3110,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>35</v>
       </c>
@@ -3125,7 +3133,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>35</v>
       </c>
@@ -3148,7 +3156,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -3180,7 +3188,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -3203,7 +3211,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -3226,7 +3234,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -3258,7 +3266,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -3278,7 +3286,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>37</v>
       </c>
@@ -3301,7 +3309,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -3324,7 +3332,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -3347,7 +3355,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -3370,7 +3378,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -3393,7 +3401,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -3416,7 +3424,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -3448,7 +3456,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -3471,7 +3479,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>41</v>
       </c>
@@ -3494,7 +3502,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>41</v>
       </c>
@@ -3517,7 +3525,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>41</v>
       </c>
@@ -3540,7 +3548,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -3572,7 +3580,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -3592,7 +3600,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>46</v>
       </c>
@@ -3624,7 +3632,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>46</v>
       </c>
@@ -3656,7 +3664,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>46</v>
       </c>
@@ -3688,7 +3696,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -3711,7 +3719,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -3734,7 +3742,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -3757,7 +3765,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -3780,7 +3788,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -3803,7 +3811,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>47</v>
       </c>
@@ -3826,7 +3834,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>47</v>
       </c>
@@ -3849,7 +3857,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>47</v>
       </c>
@@ -3872,7 +3880,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>47</v>
       </c>
@@ -3895,7 +3903,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>47</v>
       </c>
@@ -3918,7 +3926,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>47</v>
       </c>
@@ -3941,7 +3949,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>47</v>
       </c>
@@ -3964,7 +3972,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>47</v>
       </c>
@@ -3987,7 +3995,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>47</v>
       </c>
@@ -4010,7 +4018,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>47</v>
       </c>
@@ -4033,7 +4041,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>47</v>
       </c>
@@ -4056,7 +4064,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>47</v>
       </c>
@@ -4079,7 +4087,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>47</v>
       </c>
@@ -4102,7 +4110,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>47</v>
       </c>
@@ -4125,7 +4133,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>47</v>
       </c>
@@ -4148,7 +4156,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>47</v>
       </c>
@@ -4171,7 +4179,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>47</v>
       </c>
@@ -4194,7 +4202,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>47</v>
       </c>
@@ -4217,7 +4225,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>47</v>
       </c>
@@ -4240,7 +4248,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>47</v>
       </c>
@@ -4263,7 +4271,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>47</v>
       </c>
@@ -4295,7 +4303,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>48</v>
       </c>
@@ -4315,7 +4323,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>48</v>
       </c>
@@ -4335,7 +4343,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>48</v>
       </c>
@@ -4358,7 +4366,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>48</v>
       </c>
@@ -4381,7 +4389,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>49</v>
       </c>
@@ -4401,7 +4409,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>49</v>
       </c>
@@ -4424,7 +4432,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>49</v>
       </c>
@@ -4447,7 +4455,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>52</v>
       </c>
@@ -4467,7 +4475,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>52</v>
       </c>
@@ -4490,7 +4498,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>52</v>
       </c>
@@ -4522,7 +4530,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>54</v>
       </c>
@@ -4542,7 +4550,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>54</v>
       </c>
@@ -4565,7 +4573,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>54</v>
       </c>
@@ -4588,7 +4596,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>54</v>
       </c>
@@ -4611,7 +4619,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>55</v>
       </c>
@@ -4634,7 +4642,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>55</v>
       </c>
@@ -4657,7 +4665,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>55</v>
       </c>
@@ -4689,7 +4697,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>55</v>
       </c>
@@ -4721,7 +4729,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>55</v>
       </c>
@@ -4753,7 +4761,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>55</v>
       </c>
@@ -4785,7 +4793,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>56</v>
       </c>
@@ -4805,7 +4813,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>56</v>
       </c>
@@ -4825,7 +4833,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>56</v>
       </c>
@@ -4848,7 +4856,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>57</v>
       </c>
@@ -4880,7 +4888,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>57</v>
       </c>
@@ -4912,7 +4920,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>61</v>
       </c>
@@ -4933,6 +4941,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J94" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="FP"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/LexIA_Diario/config/metricas_julio_2026.xlsx
+++ b/LexIA_Diario/config/metricas_julio_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/Interbank/LexIA_Diario/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_1C814E6DB7975EF061BA440EDA1E6772385F6ABF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C7E1D29-FE23-4EB7-B8AD-E0ECE1CCAEC1}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_1C814E6DB7975EF061BA440EDA1E6772385F6ABF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD20364D-7AFA-40AA-BCE6-A0F4B6A1CCDA}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">norma_por_norma!$A$1:$J$94</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="326">
   <si>
     <t>metrica</t>
   </si>
@@ -49,6 +65,12 @@
   </si>
   <si>
     <t>dias_sin_validacion_en_excel</t>
+  </si>
+  <si>
+    <t>Analista si</t>
+  </si>
+  <si>
+    <t>Analista no</t>
   </si>
   <si>
     <t>dias_sin_reporte</t>
@@ -1353,13 +1375,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.26953125" customWidth="1"/>
+    <col min="7" max="7" width="14.1796875" customWidth="1"/>
+    <col min="8" max="8" width="13.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1367,7 +1391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1375,7 +1399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -1383,105 +1407,120 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="G4">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="G6">
+        <v>38</v>
+      </c>
+      <c r="H6">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B8">
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B9">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B10">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B11">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B12">
         <v>0.32098765432098758</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B13">
         <v>0.68421052631578949</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>0.43697478991596639</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B15">
         <v>0.3708898944193062</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B16">
         <v>0.60277777777777775</v>
@@ -1489,7 +1528,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B17">
         <v>0.59396143979477312</v>
@@ -1510,40 +1549,40 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
@@ -1551,7 +1590,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -1586,10 +1625,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -1624,10 +1663,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
         <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>32</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -1662,10 +1701,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -1700,10 +1739,10 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1738,10 +1777,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1773,10 +1812,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1802,10 +1841,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1840,10 +1879,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1878,10 +1917,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -1907,10 +1946,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1936,10 +1975,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1965,10 +2004,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1994,10 +2033,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -2032,10 +2071,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -2070,10 +2109,10 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -2105,10 +2144,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -2140,10 +2179,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -2169,10 +2208,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -2198,10 +2237,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -2236,10 +2275,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B22" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -2265,10 +2304,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -2300,10 +2339,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24">
         <v>4</v>
@@ -2338,10 +2377,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -2373,10 +2412,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -2411,10 +2450,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -2440,10 +2479,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -2469,10 +2508,10 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -2498,10 +2537,10 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -2533,7 +2572,7 @@
         <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -2573,77 +2612,77 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
@@ -2651,31 +2690,31 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
@@ -2683,31 +2722,31 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" t="s">
         <v>87</v>
       </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" t="s">
-        <v>84</v>
-      </c>
-      <c r="F5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" t="s">
-        <v>85</v>
-      </c>
       <c r="H5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
@@ -2715,31 +2754,31 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
@@ -2747,2204 +2786,2204 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" t="s">
         <v>94</v>
       </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" t="s">
-        <v>91</v>
-      </c>
-      <c r="F7" t="s">
-        <v>92</v>
-      </c>
       <c r="G7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" t="s">
-        <v>79</v>
-      </c>
       <c r="H10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="J11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H12" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J13" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I14" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" t="s">
         <v>120</v>
       </c>
-      <c r="I14" t="s">
-        <v>121</v>
-      </c>
-      <c r="J14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H15" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D16" t="s">
-        <v>125</v>
-      </c>
-      <c r="F16" t="s">
-        <v>79</v>
-      </c>
       <c r="H16" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="I17" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J17" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F18" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H18" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I18" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J18" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G19" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H19" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I19" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F20" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" t="s">
-        <v>79</v>
-      </c>
       <c r="H20" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J20" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E22" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F22" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I22" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J22" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J24" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D25" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E25" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I25" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J25" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E26" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G26" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I26" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D27" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F27" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J27" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F28" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J28" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J29" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J30" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J31" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D32" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F32" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H32" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J32" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G33" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J33" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D34" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F34" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" t="s">
+        <v>80</v>
+      </c>
+      <c r="F35" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" t="s">
-        <v>177</v>
-      </c>
-      <c r="D35" t="s">
-        <v>78</v>
-      </c>
-      <c r="F35" t="s">
-        <v>79</v>
-      </c>
       <c r="H35" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J35" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F36" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H36" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J36" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" t="s">
+        <v>80</v>
+      </c>
+      <c r="F37" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" t="s">
-        <v>181</v>
-      </c>
-      <c r="D37" t="s">
-        <v>78</v>
-      </c>
-      <c r="F37" t="s">
-        <v>79</v>
-      </c>
       <c r="H37" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B38" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F38" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="I38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J38" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C39" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E39" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G39" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="I39" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D40" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E40" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F40" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H40" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I40" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="J40" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C41" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D41" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E41" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F41" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H41" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I41" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J41" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C42" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E42" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F42" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G42" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H42" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="I42" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J42" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C43" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D43" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F43" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H43" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J43" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C44" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D44" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F44" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H44" t="s">
+        <v>207</v>
+      </c>
+      <c r="J44" t="s">
         <v>205</v>
       </c>
-      <c r="J44" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C45" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D45" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F45" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H45" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J45" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C46" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H46" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J46" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C47" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D47" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F47" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H47" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J47" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C48" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D48" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F48" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H48" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="J48" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C49" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D49" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F49" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H49" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J49" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C50" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D50" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F50" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H50" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J50" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C51" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D51" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F51" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H51" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="J51" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C52" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D52" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F52" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H52" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J52" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D53" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H53" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J53" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C54" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D54" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F54" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H54" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="J54" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D55" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F55" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H55" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J55" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D56" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F56" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H56" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J56" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C57" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D57" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F57" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H57" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J57" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D58" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F58" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H58" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="J58" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D59" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F59" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H59" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J59" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D60" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F60" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H60" t="s">
+        <v>239</v>
+      </c>
+      <c r="J60" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>49</v>
+      </c>
+      <c r="B61" t="s">
+        <v>78</v>
+      </c>
+      <c r="C61" t="s">
+        <v>240</v>
+      </c>
+      <c r="D61" t="s">
+        <v>109</v>
+      </c>
+      <c r="F61" t="s">
+        <v>173</v>
+      </c>
+      <c r="H61" t="s">
+        <v>241</v>
+      </c>
+      <c r="J61" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>49</v>
+      </c>
+      <c r="B62" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" t="s">
+        <v>242</v>
+      </c>
+      <c r="D62" t="s">
+        <v>109</v>
+      </c>
+      <c r="F62" t="s">
+        <v>173</v>
+      </c>
+      <c r="H62" t="s">
         <v>237</v>
       </c>
-      <c r="J60" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>47</v>
-      </c>
-      <c r="B61" t="s">
-        <v>76</v>
-      </c>
-      <c r="C61" t="s">
-        <v>238</v>
-      </c>
-      <c r="D61" t="s">
-        <v>107</v>
-      </c>
-      <c r="F61" t="s">
-        <v>171</v>
-      </c>
-      <c r="H61" t="s">
-        <v>239</v>
-      </c>
-      <c r="J61" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>47</v>
-      </c>
-      <c r="B62" t="s">
-        <v>76</v>
-      </c>
-      <c r="C62" t="s">
-        <v>240</v>
-      </c>
-      <c r="D62" t="s">
-        <v>107</v>
-      </c>
-      <c r="F62" t="s">
-        <v>171</v>
-      </c>
-      <c r="H62" t="s">
-        <v>235</v>
-      </c>
       <c r="J62" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D63" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F63" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H63" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J63" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C64" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H64" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J64" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C65" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D65" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F65" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H65" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J65" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D66" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F66" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H66" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J66" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C67" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D67" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F67" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H67" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J67" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B68" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C68" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D68" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E68" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F68" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G68" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H68" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="I68" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J68" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C69" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E69" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G69" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I69" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E70" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G70" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I70" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B71" t="s">
+        <v>78</v>
+      </c>
+      <c r="C71" t="s">
+        <v>263</v>
+      </c>
+      <c r="D71" t="s">
+        <v>264</v>
+      </c>
+      <c r="F71" t="s">
+        <v>173</v>
+      </c>
+      <c r="H71" t="s">
+        <v>265</v>
+      </c>
+      <c r="J71" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>50</v>
+      </c>
+      <c r="B72" t="s">
+        <v>78</v>
+      </c>
+      <c r="C72" t="s">
+        <v>266</v>
+      </c>
+      <c r="D72" t="s">
+        <v>267</v>
+      </c>
+      <c r="F72" t="s">
+        <v>94</v>
+      </c>
+      <c r="H72" t="s">
+        <v>268</v>
+      </c>
+      <c r="J72" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>51</v>
+      </c>
+      <c r="B73" t="s">
+        <v>73</v>
+      </c>
+      <c r="C73" t="s">
+        <v>269</v>
+      </c>
+      <c r="E73" t="s">
+        <v>151</v>
+      </c>
+      <c r="G73" t="s">
         <v>76</v>
       </c>
-      <c r="C71" t="s">
-        <v>261</v>
-      </c>
-      <c r="D71" t="s">
-        <v>262</v>
-      </c>
-      <c r="F71" t="s">
-        <v>171</v>
-      </c>
-      <c r="H71" t="s">
-        <v>263</v>
-      </c>
-      <c r="J71" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>48</v>
-      </c>
-      <c r="B72" t="s">
+      <c r="I73" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>51</v>
+      </c>
+      <c r="B74" t="s">
+        <v>78</v>
+      </c>
+      <c r="C74" t="s">
+        <v>271</v>
+      </c>
+      <c r="D74" t="s">
+        <v>264</v>
+      </c>
+      <c r="F74" t="s">
+        <v>94</v>
+      </c>
+      <c r="H74" t="s">
+        <v>272</v>
+      </c>
+      <c r="J74" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>51</v>
+      </c>
+      <c r="B75" t="s">
+        <v>78</v>
+      </c>
+      <c r="C75" t="s">
+        <v>274</v>
+      </c>
+      <c r="D75" t="s">
+        <v>275</v>
+      </c>
+      <c r="F75" t="s">
+        <v>94</v>
+      </c>
+      <c r="H75" t="s">
+        <v>276</v>
+      </c>
+      <c r="J75" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>54</v>
+      </c>
+      <c r="B76" t="s">
+        <v>73</v>
+      </c>
+      <c r="C76" t="s">
+        <v>277</v>
+      </c>
+      <c r="E76" t="s">
+        <v>154</v>
+      </c>
+      <c r="G76" t="s">
         <v>76</v>
       </c>
-      <c r="C72" t="s">
+      <c r="I76" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>54</v>
+      </c>
+      <c r="B77" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" t="s">
+        <v>279</v>
+      </c>
+      <c r="D77" t="s">
         <v>264</v>
       </c>
-      <c r="D72" t="s">
-        <v>265</v>
-      </c>
-      <c r="F72" t="s">
-        <v>92</v>
-      </c>
-      <c r="H72" t="s">
-        <v>266</v>
-      </c>
-      <c r="J72" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>49</v>
-      </c>
-      <c r="B73" t="s">
-        <v>71</v>
-      </c>
-      <c r="C73" t="s">
-        <v>267</v>
-      </c>
-      <c r="E73" t="s">
-        <v>149</v>
-      </c>
-      <c r="G73" t="s">
-        <v>74</v>
-      </c>
-      <c r="I73" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>49</v>
-      </c>
-      <c r="B74" t="s">
-        <v>76</v>
-      </c>
-      <c r="C74" t="s">
-        <v>269</v>
-      </c>
-      <c r="D74" t="s">
-        <v>262</v>
-      </c>
-      <c r="F74" t="s">
-        <v>92</v>
-      </c>
-      <c r="H74" t="s">
-        <v>270</v>
-      </c>
-      <c r="J74" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>49</v>
-      </c>
-      <c r="B75" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" t="s">
-        <v>272</v>
-      </c>
-      <c r="D75" t="s">
-        <v>273</v>
-      </c>
-      <c r="F75" t="s">
-        <v>92</v>
-      </c>
-      <c r="H75" t="s">
-        <v>274</v>
-      </c>
-      <c r="J75" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>52</v>
-      </c>
-      <c r="B76" t="s">
-        <v>71</v>
-      </c>
-      <c r="C76" t="s">
-        <v>275</v>
-      </c>
-      <c r="E76" t="s">
-        <v>152</v>
-      </c>
-      <c r="G76" t="s">
-        <v>74</v>
-      </c>
-      <c r="I76" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>52</v>
-      </c>
-      <c r="B77" t="s">
-        <v>76</v>
-      </c>
-      <c r="C77" t="s">
-        <v>277</v>
-      </c>
-      <c r="D77" t="s">
-        <v>262</v>
-      </c>
       <c r="F77" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H77" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J77" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B78" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D78" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E78" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F78" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G78" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H78" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I78" t="s">
+        <v>284</v>
+      </c>
+      <c r="J78" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>56</v>
+      </c>
+      <c r="B79" t="s">
+        <v>73</v>
+      </c>
+      <c r="C79" t="s">
+        <v>285</v>
+      </c>
+      <c r="E79" t="s">
         <v>282</v>
       </c>
-      <c r="J78" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>54</v>
-      </c>
-      <c r="B79" t="s">
-        <v>71</v>
-      </c>
-      <c r="C79" t="s">
-        <v>283</v>
-      </c>
-      <c r="E79" t="s">
-        <v>280</v>
-      </c>
       <c r="G79" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I79" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B80" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C80" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D80" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F80" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H80" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J80" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B81" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C81" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D81" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F81" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H81" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J81" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B82" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C82" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D82" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F82" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H82" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J82" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B83" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C83" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D83" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F83" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H83" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="J83" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B84" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C84" t="s">
+        <v>298</v>
+      </c>
+      <c r="D84" t="s">
         <v>296</v>
       </c>
-      <c r="D84" t="s">
-        <v>294</v>
-      </c>
       <c r="F84" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H84" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J84" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B85" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C85" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D85" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E85" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F85" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G85" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H85" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I85" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J85" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B86" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C86" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D86" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E86" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F86" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G86" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H86" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="I86" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J86" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B87" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C87" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D87" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E87" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F87" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G87" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H87" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="I87" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J87" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B88" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C88" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D88" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E88" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F88" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G88" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H88" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I88" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J88" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C89" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E89" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G89" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I89" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B90" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C90" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E90" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G90" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I90" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B91" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C91" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D91" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F91" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H91" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J91" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B92" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C92" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D92" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E92" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F92" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G92" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H92" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="I92" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="J92" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B93" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C93" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D93" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E93" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F93" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G93" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H93" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="I93" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J93" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B94" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C94" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E94" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G94" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I94" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J94" xr:uid="{00000000-0001-0000-0200-000000000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="FP"/>
+        <filter val="FN"/>
       </filters>
     </filterColumn>
   </autoFilter>
